--- a/02_DIA_inicio_2026_analisis_assets/rbd_25173_esc-basica-municipal-risopatron_nt2_nucleos.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_25173_esc-basica-municipal-risopatron_nt2_nucleos.xlsx
@@ -775,13 +775,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0602712A-E7BF-4EF1-8FB0-68756CC10E62}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{18157282-DE59-49D7-BCFF-F4F3570A5AE6}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{633BBC87-7DE3-40C1-848A-9432D5D483CE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ADA96A83-41B9-4A8C-AF4C-21E43FF61CF0}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{61D66385-8317-444C-A4BD-8B37ADC05B5B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8B5B3571-E618-4526-8F56-4FE8492FE8F3}"/>
 </file>